--- a/Tests/viwTests/Fixtures/sample.xlsx
+++ b/Tests/viwTests/Fixtures/sample.xlsx
@@ -908,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1092,6 +1092,29 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>func2</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>IF(B2&gt;100,"many","few")</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>ROUND(C5/7,2)</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>COUNTA(A2:A9)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>TEXT(D2,"#,##0")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
